--- a/public/translations.xlsx
+++ b/public/translations.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="493">
   <si>
     <t>key</t>
   </si>
@@ -1391,13 +1391,112 @@
   </si>
   <si>
     <t>Командабыздын тазалык жана тартип орнотуп жатканын кыскача видеодон көрүңүз.</t>
+  </si>
+  <si>
+    <t>Онлайн расчет</t>
+  </si>
+  <si>
+    <t>Онлайн эсептөө</t>
+  </si>
+  <si>
+    <t>Калькулятор стоимости</t>
+  </si>
+  <si>
+    <t>Баа калькулятору</t>
+  </si>
+  <si>
+    <t>Узнайте примерную стоимость услуг за пару кликов.</t>
+  </si>
+  <si>
+    <t>Кызматтардын болжолдуу баасын бир нече чыкылдатуу менен билип алыңыз.</t>
+  </si>
+  <si>
+    <t>Химиялык тазалоо</t>
+  </si>
+  <si>
+    <t>Тазалоо түрү</t>
+  </si>
+  <si>
+    <t>Бөлмөнүн аянты</t>
+  </si>
+  <si>
+    <t>Диваны (посадочные места)</t>
+  </si>
+  <si>
+    <t>Дивандар (отуруучу орундар)</t>
+  </si>
+  <si>
+    <t>Отургучтар / Креслолор</t>
+  </si>
+  <si>
+    <t>от 650 с / место</t>
+  </si>
+  <si>
+    <t>650 с баштап / орун</t>
+  </si>
+  <si>
+    <t>от 250 с / шт</t>
+  </si>
+  <si>
+    <t>250 с баштап / даана</t>
+  </si>
+  <si>
+    <t>Площадь фасада</t>
+  </si>
+  <si>
+    <t>Фасаддын аянты</t>
+  </si>
+  <si>
+    <t>Время аренды (в часах)</t>
+  </si>
+  <si>
+    <t>Ижара убактысы (саат менен)</t>
+  </si>
+  <si>
+    <t>Минимальный заказ - 2 часа</t>
+  </si>
+  <si>
+    <t>Минималдуу буйрутма - 2 саат</t>
+  </si>
+  <si>
+    <t>Генералдык тазалоо</t>
+  </si>
+  <si>
+    <t>Срочная уборка</t>
+  </si>
+  <si>
+    <t>Шашылыш тазалоо</t>
+  </si>
+  <si>
+    <t>Фасаддарды жуу</t>
+  </si>
+  <si>
+    <t>При необходимости используется спецтехника (автовышка).</t>
+  </si>
+  <si>
+    <t>Зарыл болгон учурда атайын техника (автовышка) колдонулат.</t>
+  </si>
+  <si>
+    <t>с</t>
+  </si>
+  <si>
+    <t>* Точная цена формируется после оценки менеджером</t>
+  </si>
+  <si>
+    <t>* Так баасы менеджер баалагандан кийин түзүлөт</t>
+  </si>
+  <si>
+    <t>Заказать за</t>
+  </si>
+  <si>
+    <t>Буйрутма берүү:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1422,6 +1521,10 @@
       <color rgb="FF1F1F1F"/>
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
+    <font>
+      <color rgb="FF444746"/>
+      <name val="&quot;Google Sans Text&quot;"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1437,7 +1540,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1454,6 +1557,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -3468,6 +3574,319 @@
         <v>459</v>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" s="4"/>
+      <c r="B167" s="4"/>
+      <c r="C167" s="4"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>492</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="A8"/>
